--- a/stories/arbres/TREE-DIF-038.xlsx
+++ b/stories/arbres/TREE-DIF-038.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Noé est avec maman, dans le salon. Noé a envie de jouer. maman est là, tout près. On va apprendre : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé écoute maman. Noé entend les mots : laisser le temps.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Noé va vers le bac à sable. Ça sent le pain chaud. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Noé se souvient : laisser le temps. Voici le geste : attendre la fin de la phrase. On attend son tour. maman dit : je suis là. On reste ensemble.</t>
+          <t>Noé va vers le bac à sable. Ça sent le pain chaud. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Noé se souvient : laisser le temps. Voici le geste : attendre la fin de la phrase. On attend son tour. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,12 @@
         <v>12</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Noé va vers le bac à sable. Ça sent le pain chaud. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Noé se souvient : laisser le temps. Voici le geste : attendre la fin de la phrase. On attend son tour.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1862,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Laisser le temps à l'autre de finir sa phrase.</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2035,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : attendre la fin de la phrase. Noé respire. Noé retient : laisser le temps. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2183,6 +2226,11 @@
         <v>12</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2345,6 +2393,11 @@
         <v>12</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi le ballon. Le sol est un peu froid. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Noé répète tout bas : laisser le temps. On se tait une seconde. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2533,6 +2586,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2697,6 +2755,11 @@
         <v>12</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Tom. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de le bac à sable, le ballon et Tom. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2859,6 +2922,11 @@
         <v>12</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3021,6 +3089,11 @@
         <v>12</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Léa. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le ballon et Léa. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3183,6 +3256,11 @@
         <v>12</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3345,6 +3423,11 @@
         <v>12</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Sami. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de le bac à sable, le ballon et Sami. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3507,6 +3590,11 @@
         <v>12</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3669,6 +3757,11 @@
         <v>12</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi le seau. Une feuille tombe. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Noé répète tout bas : laisser le temps. On se tient la main. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3857,6 +3950,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -4021,6 +4119,11 @@
         <v>12</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Tom. La lumière est claire. On attend son tour. Cette fin-là est celle de le bac à sable, le seau et Tom. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4183,6 +4286,11 @@
         <v>12</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4345,6 +4453,11 @@
         <v>12</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Léa. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le seau et Léa. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4507,6 +4620,11 @@
         <v>12</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4669,6 +4787,11 @@
         <v>12</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Sami. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de le bac à sable, le seau et Sami. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4831,6 +4954,11 @@
         <v>12</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4993,6 +5121,11 @@
         <v>12</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi le doudou. L'eau coule, tout petit bruit. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Noé répète tout bas : laisser le temps. On range un objet. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5181,6 +5314,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -5345,6 +5483,11 @@
         <v>12</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Tom. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de le bac à sable, le doudou et Tom. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5507,6 +5650,11 @@
         <v>12</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5669,6 +5817,11 @@
         <v>12</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Léa. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le doudou et Léa. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5831,6 +5984,11 @@
         <v>12</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5993,6 +6151,11 @@
         <v>12</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Sami. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de le bac à sable, le doudou et Sami. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6155,6 +6318,11 @@
         <v>12</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6179,7 +6347,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Noé va vers le toboggan. Le vent est doux. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Noé se souvient : laisser le temps. Voici le geste : attendre la fin de la phrase. On montre du doigt, sans courir. maman dit : je suis là. On reste ensemble.</t>
+          <t>Noé va vers le toboggan. Le vent est doux. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Noé se souvient : laisser le temps. Voici le geste : attendre la fin de la phrase. On montre du doigt, sans courir. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6317,6 +6485,12 @@
         <v>12</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Noé va vers le toboggan. Le vent est doux. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Noé se souvient : laisser le temps. Voici le geste : attendre la fin de la phrase. On montre du doigt, sans courir.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6497,6 +6671,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Laisser le temps à l'autre de finir sa phrase.</t>
         </is>
       </c>
     </row>
@@ -6665,6 +6844,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : attendre la fin de la phrase. Noé respire. Noé retient : laisser le temps. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6851,6 +7035,11 @@
         <v>12</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7013,6 +7202,11 @@
         <v>12</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi le ballon. Un vélo passe au loin. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Noé répète tout bas : laisser le temps. On se tait une seconde. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7201,6 +7395,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7365,6 +7564,11 @@
         <v>12</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Tom. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le ballon et Tom. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7527,6 +7731,11 @@
         <v>12</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7689,6 +7898,11 @@
         <v>12</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Léa. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de le toboggan, le ballon et Léa. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7851,6 +8065,11 @@
         <v>12</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8013,6 +8232,11 @@
         <v>12</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Sami. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de le toboggan, le ballon et Sami. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8175,6 +8399,11 @@
         <v>12</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8337,6 +8566,11 @@
         <v>12</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi le seau. La lumière est claire. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Noé répète tout bas : laisser le temps. On se tient la main. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8525,6 +8759,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -8689,6 +8928,11 @@
         <v>12</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Tom. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le seau et Tom. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8851,6 +9095,11 @@
         <v>12</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9013,6 +9262,11 @@
         <v>12</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Léa. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de le toboggan, le seau et Léa. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9175,6 +9429,11 @@
         <v>12</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9337,6 +9596,11 @@
         <v>12</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Sami. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de le toboggan, le seau et Sami. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9499,6 +9763,11 @@
         <v>12</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9661,6 +9930,11 @@
         <v>12</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi le doudou. Il y a des miettes sur la table. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Noé répète tout bas : laisser le temps. On range un objet. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9849,6 +10123,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -10013,6 +10292,11 @@
         <v>12</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Tom. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le doudou et Tom. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10175,6 +10459,11 @@
         <v>12</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10337,6 +10626,11 @@
         <v>12</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Léa. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de le toboggan, le doudou et Léa. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10499,6 +10793,11 @@
         <v>12</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10661,6 +10960,11 @@
         <v>12</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Sami. La couverture est douce. On se tait une seconde. Cette fin-là est celle de le toboggan, le doudou et Sami. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10823,6 +11127,11 @@
         <v>12</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10847,7 +11156,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Noé va vers les balançoires. Le sol est un peu froid. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Noé se souvient : laisser le temps. Voici le geste : attendre la fin de la phrase. On rit un peu. maman dit : je suis là. On reste ensemble.</t>
+          <t>Noé va vers les balançoires. Le sol est un peu froid. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Noé se souvient : laisser le temps. Voici le geste : attendre la fin de la phrase. On rit un peu. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10985,6 +11294,12 @@
         <v>12</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Noé va vers les balançoires. Le sol est un peu froid. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Noé se souvient : laisser le temps. Voici le geste : attendre la fin de la phrase. On rit un peu.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11165,6 +11480,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Laisser le temps à l'autre de finir sa phrase.</t>
         </is>
       </c>
     </row>
@@ -11333,6 +11653,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : attendre la fin de la phrase. Noé respire. Noé retient : laisser le temps. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11519,6 +11844,11 @@
         <v>12</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11681,6 +12011,11 @@
         <v>12</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi le ballon. Un chat miaule une fois. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Noé répète tout bas : laisser le temps. On se tait une seconde. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11869,6 +12204,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -12033,6 +12373,11 @@
         <v>12</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Tom. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de les balançoires, le ballon et Tom. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12195,6 +12540,11 @@
         <v>12</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12357,6 +12707,11 @@
         <v>12</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Léa. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de les balançoires, le ballon et Léa. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12519,6 +12874,11 @@
         <v>12</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12681,6 +13041,11 @@
         <v>12</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Sami. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de les balançoires, le ballon et Sami. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12843,6 +13208,11 @@
         <v>12</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13005,6 +13375,11 @@
         <v>12</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi le seau. Les chaussures font toc toc. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Noé répète tout bas : laisser le temps. On se tient la main. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13193,6 +13568,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -13357,6 +13737,11 @@
         <v>12</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Tom. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de les balançoires, le seau et Tom. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13519,6 +13904,11 @@
         <v>12</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13681,6 +14071,11 @@
         <v>12</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Léa. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de les balançoires, le seau et Léa. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13843,6 +14238,11 @@
         <v>12</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14005,6 +14405,11 @@
         <v>12</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Sami. La couverture est douce. On se tient la main. Cette fin-là est celle de les balançoires, le seau et Sami. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14167,6 +14572,11 @@
         <v>12</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14329,6 +14739,11 @@
         <v>12</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi le doudou. La couverture est douce. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Noé répète tout bas : laisser le temps. On range un objet. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14517,6 +14932,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -14681,6 +15101,11 @@
         <v>12</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Tom. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de les balançoires, le doudou et Tom. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14843,6 +15268,11 @@
         <v>12</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15005,6 +15435,11 @@
         <v>12</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Léa. La couverture est douce. On se tait une seconde. Cette fin-là est celle de les balançoires, le doudou et Léa. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15167,6 +15602,11 @@
         <v>12</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15329,6 +15769,11 @@
         <v>12</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint Sami. On entend un oiseau. On se tient la main. Cette fin-là est celle de les balançoires, le doudou et Sami. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15491,6 +15936,11 @@
         <v>12</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15509,7 +15959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15582,6 +16032,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-DIF-038.xlsx
+++ b/stories/arbres/TREE-DIF-038.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Noé est avec maman, dans le salon. Noé a envie de jouer. maman est là, tout près. On va apprendre : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé écoute maman. Noé entend les mots : laisser le temps.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1869,6 +1877,7 @@
           <t>narrateur|Que fait-on ? Laisser le temps à l'autre de finir sa phrase.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2040,6 +2049,7 @@
           <t>narrateur|Oui. Voici le geste : attendre la fin de la phrase. Noé respire. Noé retient : laisser le temps. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2231,6 +2241,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2398,6 +2409,7 @@
           <t>narrateur|Noé a choisi le ballon. Le sol est un peu froid. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Noé répète tout bas : laisser le temps. On se tait une seconde. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2593,6 +2605,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2760,6 +2773,7 @@
           <t>narrateur|Noé rejoint Tom. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de le bac à sable, le ballon et Tom. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2927,6 +2941,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3094,6 +3109,7 @@
           <t>narrateur|Noé rejoint Léa. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le ballon et Léa. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3261,6 +3277,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3428,6 +3445,7 @@
           <t>narrateur|Noé rejoint Sami. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de le bac à sable, le ballon et Sami. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3595,6 +3613,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3762,6 +3781,7 @@
           <t>narrateur|Noé a choisi le seau. Une feuille tombe. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Noé répète tout bas : laisser le temps. On se tient la main. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3957,6 +3977,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4124,6 +4145,7 @@
           <t>narrateur|Noé rejoint Tom. La lumière est claire. On attend son tour. Cette fin-là est celle de le bac à sable, le seau et Tom. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4291,6 +4313,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4458,6 +4481,7 @@
           <t>narrateur|Noé rejoint Léa. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le seau et Léa. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4625,6 +4649,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4792,6 +4817,7 @@
           <t>narrateur|Noé rejoint Sami. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de le bac à sable, le seau et Sami. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4959,6 +4985,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5126,6 +5153,7 @@
           <t>narrateur|Noé a choisi le doudou. L'eau coule, tout petit bruit. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Noé répète tout bas : laisser le temps. On range un objet. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5321,6 +5349,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5488,6 +5517,7 @@
           <t>narrateur|Noé rejoint Tom. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de le bac à sable, le doudou et Tom. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5655,6 +5685,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5822,6 +5853,7 @@
           <t>narrateur|Noé rejoint Léa. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de le bac à sable, le doudou et Léa. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5989,6 +6021,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6156,6 +6189,7 @@
           <t>narrateur|Noé rejoint Sami. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de le bac à sable, le doudou et Sami. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6323,6 +6357,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6491,6 +6526,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6678,6 +6714,7 @@
           <t>narrateur|Que fait-on ? Laisser le temps à l'autre de finir sa phrase.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6849,6 +6886,7 @@
           <t>narrateur|Oui. Voici le geste : attendre la fin de la phrase. Noé respire. Noé retient : laisser le temps. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7040,6 +7078,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7207,6 +7246,7 @@
           <t>narrateur|Noé a choisi le ballon. Un vélo passe au loin. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Noé répète tout bas : laisser le temps. On se tait une seconde. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7402,6 +7442,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7569,6 +7610,7 @@
           <t>narrateur|Noé rejoint Tom. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le ballon et Tom. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7736,6 +7778,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7903,6 +7946,7 @@
           <t>narrateur|Noé rejoint Léa. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de le toboggan, le ballon et Léa. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8070,6 +8114,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8237,6 +8282,7 @@
           <t>narrateur|Noé rejoint Sami. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de le toboggan, le ballon et Sami. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8404,6 +8450,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8571,6 +8618,7 @@
           <t>narrateur|Noé a choisi le seau. La lumière est claire. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Noé répète tout bas : laisser le temps. On se tient la main. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8766,6 +8814,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8933,6 +8982,7 @@
           <t>narrateur|Noé rejoint Tom. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le seau et Tom. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9100,6 +9150,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9267,6 +9318,7 @@
           <t>narrateur|Noé rejoint Léa. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de le toboggan, le seau et Léa. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9434,6 +9486,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9601,6 +9654,7 @@
           <t>narrateur|Noé rejoint Sami. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de le toboggan, le seau et Sami. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9768,6 +9822,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9935,6 +9990,7 @@
           <t>narrateur|Noé a choisi le doudou. Il y a des miettes sur la table. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Noé répète tout bas : laisser le temps. On range un objet. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10130,6 +10186,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10297,6 +10354,7 @@
           <t>narrateur|Noé rejoint Tom. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de le toboggan, le doudou et Tom. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10464,6 +10522,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10631,6 +10690,7 @@
           <t>narrateur|Noé rejoint Léa. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de le toboggan, le doudou et Léa. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10798,6 +10858,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10965,6 +11026,7 @@
           <t>narrateur|Noé rejoint Sami. La couverture est douce. On se tait une seconde. Cette fin-là est celle de le toboggan, le doudou et Sami. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11132,6 +11194,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11300,6 +11363,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11487,6 +11551,7 @@
           <t>narrateur|Que fait-on ? Laisser le temps à l'autre de finir sa phrase.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11658,6 +11723,7 @@
           <t>narrateur|Oui. Voici le geste : attendre la fin de la phrase. Noé respire. Noé retient : laisser le temps. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11849,6 +11915,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12016,6 +12083,7 @@
           <t>narrateur|Noé a choisi le ballon. Un chat miaule une fois. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Noé répète tout bas : laisser le temps. On se tait une seconde. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12211,6 +12279,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12378,6 +12447,7 @@
           <t>narrateur|Noé rejoint Tom. Il y a des miettes sur la table. On rit un peu. Cette fin-là est celle de les balançoires, le ballon et Tom. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12545,6 +12615,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12712,6 +12783,7 @@
           <t>narrateur|Noé rejoint Léa. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de les balançoires, le ballon et Léa. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12879,6 +12951,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13046,6 +13119,7 @@
           <t>narrateur|Noé rejoint Sami. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de les balançoires, le ballon et Sami. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13213,6 +13287,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13380,6 +13455,7 @@
           <t>narrateur|Noé a choisi le seau. Les chaussures font toc toc. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Noé répète tout bas : laisser le temps. On se tient la main. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13575,6 +13651,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13742,6 +13819,7 @@
           <t>narrateur|Noé rejoint Tom. Un chat miaule une fois. On rit un peu. Cette fin-là est celle de les balançoires, le seau et Tom. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13909,6 +13987,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14076,6 +14155,7 @@
           <t>narrateur|Noé rejoint Léa. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de les balançoires, le seau et Léa. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14243,6 +14323,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14410,6 +14491,7 @@
           <t>narrateur|Noé rejoint Sami. La couverture est douce. On se tient la main. Cette fin-là est celle de les balançoires, le seau et Sami. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14577,6 +14659,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14744,6 +14827,7 @@
           <t>narrateur|Noé a choisi le doudou. La couverture est douce. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : attendre la fin de la phrase. Noé répète tout bas : laisser le temps. On range un objet. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14939,6 +15023,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15106,6 +15191,7 @@
           <t>narrateur|Noé rejoint Tom. Les chaussures font toc toc. On rit un peu. Cette fin-là est celle de les balançoires, le doudou et Tom. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15273,6 +15359,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15440,6 +15527,7 @@
           <t>narrateur|Noé rejoint Léa. La couverture est douce. On se tait une seconde. Cette fin-là est celle de les balançoires, le doudou et Léa. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15607,6 +15695,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15774,6 +15863,7 @@
           <t>narrateur|Noé rejoint Sami. On entend un oiseau. On se tient la main. Cette fin-là est celle de les balançoires, le doudou et Sami. Noé a appris : Laisser le temps à l'autre de finir sa phrase. Voici le geste : attendre la fin de la phrase. Noé a entendu : laisser le temps. Noé dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15941,6 +16031,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15959,7 +16050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16039,6 +16130,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16053,7 +16158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16240,6 +16345,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-DIF-038.xlsx
+++ b/stories/arbres/TREE-DIF-038.xlsx
@@ -2306,12 +2306,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Le cheval arrive près de l'établi. Le cheval bute contre un tas de copeaux. Des copeaux cachent les tiroirs, tout jaunes. C'est ici ? C'est le tiroir. Le mot s'arrête au milieu. Lequel ? Nino referme sa bouche, tout net. Les tiroirs se ressemblent tous. Vous faites comment, tous les deux ?</t>
+          <t>Le cheval arrive près de l'établi. Le cheval bute contre un tas de copeaux. Des copeaux cachent les tiroirs, tout jaunes. C'est ici ? C'est le tiroir. Le mot s'arrête au milieu. Lequel ? Nino referme sa bouche, tout net. Les tiroirs se ressemblent tous. On fait comment, Nino ?</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Le cheval arrive près de l'établi. Le cheval bute contre un tas de copeaux. Des copeaux cachent les tiroirs, tout jaunes. C'est ici ? C'est le tiroir. Le mot s'arrête au milieu. Lequel ? Nino referme sa bouche, tout net. Les tiroirs se ressemblent tous. Vous faites comment, tous les deux ?</t>
+          <t>Le cheval arrive près de l'établi. Le cheval bute contre un tas de copeaux. Des copeaux cachent les tiroirs, tout jaunes. C'est ici ? C'est le tiroir. Le mot s'arrête au milieu. Lequel ? Nino referme sa bouche, tout net. Les tiroirs se ressemblent tous. On fait comment, Nino ?</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
 enfant-m|Lequel ?
 narrateur|Nino referme sa bouche, tout net.
 maman|Les tiroirs se ressemblent tous.
-papa|Vous faites comment, tous les deux ?</t>
+papa|On fait comment, Nino ?</t>
         </is>
       </c>
     </row>
@@ -3551,12 +3551,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>La roue du bas tient, tout nette. On s'est baissés, papa. Le haut gardera son ombre. Lavez-vous les mains, tout doux. Le bois du cheval reste un peu tiède. Nino tapote le dos, tout léger. Le bois a un peu de poussière. Une abeille passe, puis l'auvent se tait.</t>
+          <t>La roue du bas tient, tout nette. On s'est baissés, papa. Le haut gardera son ombre. Lave-toi les mains, tout doux. Le bois du cheval reste un peu tiède. Nino tapote le dos, tout léger. Le bois a un peu de poussière. Une abeille passe, puis l'auvent se tait.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>La roue du bas tient, tout nette. On s'est baissés, papa. Le haut gardera son ombre. Lavez-vous les mains, tout doux. Le bois du cheval reste un peu tiède. Nino tapote le dos, tout léger. Le bois a un peu de poussière. Une abeille passe, puis l'auvent se tait.</t>
+          <t>La roue du bas tient, tout nette. On s'est baissés, papa. Le haut gardera son ombre. Lave-toi les mains, tout doux. Le bois du cheval reste un peu tiède. Nino tapote le dos, tout léger. Le bois a un peu de poussière. Une abeille passe, puis l'auvent se tait.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -3694,7 +3694,7 @@
           <t>narrateur|La roue du bas tient, tout nette.
 enfant-m|On s'est baissés, papa.
 papa|Le haut gardera son ombre.
-maman|Lavez-vous les mains, tout doux.
+maman|Lave-toi les mains, tout doux.
 narrateur|Le bois du cheval reste un peu tiède.
 narrateur|Nino tapote le dos, tout léger.
 narrateur|Le bois a un peu de poussière.
@@ -3725,12 +3725,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Le cheval arrive près du coffre. Le cheval penche contre le couvercle lourd. Elle est là-dedans ? Elle est dans le. Maman cherche, un doigt en l'air. Le couvercle ne bouge pas, encore. Ouvre ! Nino recule d'un pas, puis attend. Le bois est trop lourd, tout seul. Vous trouvez comment ?</t>
+          <t>Le cheval arrive près du coffre. Le cheval penche contre le couvercle lourd. Elle est là-dedans ? Elle est dans le. Maman cherche, un doigt en l'air. Le couvercle ne bouge pas, encore. Ouvre ! Nino recule d'un pas, puis attend. Le bois est trop lourd, tout seul. Tu trouves comment ?</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Le cheval arrive près du coffre. Le cheval penche contre le couvercle lourd. Elle est là-dedans ? Elle est dans le. Maman cherche, un doigt en l'air. Le couvercle ne bouge pas, encore. Ouvre ! Nino recule d'un pas, puis attend. Le bois est trop lourd, tout seul. Vous trouvez comment ?</t>
+          <t>Le cheval arrive près du coffre. Le cheval penche contre le couvercle lourd. Elle est là-dedans ? Elle est dans le. Maman cherche, un doigt en l'air. Le couvercle ne bouge pas, encore. Ouvre ! Nino recule d'un pas, puis attend. Le bois est trop lourd, tout seul. Tu trouves comment ?</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
 enfant-m|Ouvre !
 narrateur|Nino recule d'un pas, puis attend.
 papa|Le bois est trop lourd, tout seul.
-maman|Vous trouvez comment ?</t>
+maman|Tu trouves comment ?</t>
         </is>
       </c>
     </row>
@@ -4445,12 +4445,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>À deux. Tes mains ici, les miennes là. Le couvercle s'ouvre, tout lent. Dans le. Nino attend, les lèvres fermées. Dans le coin. Le cheval reste contre la jambe, tout sage. Vous avez porté ensemble. La suite a eu sa place.</t>
+          <t>À deux. Tes mains ici, les miennes là. Le couvercle s'ouvre, tout lent. Dans le. Nino attend, les lèvres fermées. Dans le coin. Le cheval reste contre la jambe, tout sage. On a porté ensemble. La suite a eu sa place.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>À deux. Tes mains ici, les miennes là. Le couvercle s'ouvre, tout lent. Dans le. Nino attend, les lèvres fermées. Dans le coin. Le cheval reste contre la jambe, tout sage. Vous avez porté ensemble. La suite a eu sa place.</t>
+          <t>À deux. Tes mains ici, les miennes là. Le couvercle s'ouvre, tout lent. Dans le. Nino attend, les lèvres fermées. Dans le coin. Le cheval reste contre la jambe, tout sage. On a porté ensemble. La suite a eu sa place.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4592,7 +4592,7 @@
 narrateur|Nino attend, les lèvres fermées.
 maman|Dans le coin.
 narrateur|Le cheval reste contre la jambe, tout sage.
-papa|Vous avez porté ensemble.
+papa|On a porté ensemble.
 maman|La suite a eu sa place.</t>
         </is>
       </c>
@@ -4620,12 +4620,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>À deux, le coffre a parlé, enfin. On a porté, tous les deux. Tes mains étaient à la bonne place. Le pain vous attend. Le bois du cheval reste un peu tiède. Nino essuie une main sur son pantalon. Un grain de savon reste sur le bois. Le cheval avance, roue après roue.</t>
+          <t>À deux, le coffre a parlé, enfin. On a porté, tous les deux. Tes mains étaient à la bonne place. Le pain t'attend. Le bois du cheval reste un peu tiède. Nino essuie une main sur son pantalon. Un grain de savon reste sur le bois. Le cheval avance, roue après roue.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>À deux, le coffre a parlé, enfin. On a porté, tous les deux. Tes mains étaient à la bonne place. Le pain vous attend. Le bois du cheval reste un peu tiède. Nino essuie une main sur son pantalon. Un grain de savon reste sur le bois. Le cheval avance, roue après roue.</t>
+          <t>À deux, le coffre a parlé, enfin. On a porté, tous les deux. Tes mains étaient à la bonne place. Le pain t'attend. Le bois du cheval reste un peu tiède. Nino essuie une main sur son pantalon. Un grain de savon reste sur le bois. Le cheval avance, roue après roue.</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -4763,7 +4763,7 @@
           <t>narrateur|À deux, le coffre a parlé, enfin.
 enfant-m|On a porté, tous les deux.
 papa|Tes mains étaient à la bonne place.
-maman|Le pain vous attend.
+maman|Le pain t'attend.
 narrateur|Le bois du cheval reste un peu tiède.
 narrateur|Nino essuie une main sur son pantalon.
 narrateur|Un grain de savon reste sur le bois.
@@ -4794,12 +4794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>La cale, dessous. Je glisse le bois, tout doux. Le couvercle reste ouvert, un peu. À gauche. Nino tourne la tête, sans parler. Je la vois, au fond. Le cheval reste contre la jambe, tout sage. La cale a tenu le mot. Vous avez regardé ensemble.</t>
+          <t>La cale, dessous. Je glisse le bois, tout doux. Le couvercle reste ouvert, un peu. À gauche. Nino tourne la tête, sans parler. Je la vois, au fond. Le cheval reste contre la jambe, tout sage. La cale a tenu le mot. On a regardé ensemble.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>La cale, dessous. Je glisse le bois, tout doux. Le couvercle reste ouvert, un peu. À gauche. Nino tourne la tête, sans parler. Je la vois, au fond. Le cheval reste contre la jambe, tout sage. La cale a tenu le mot. Vous avez regardé ensemble.</t>
+          <t>La cale, dessous. Je glisse le bois, tout doux. Le couvercle reste ouvert, un peu. À gauche. Nino tourne la tête, sans parler. Je la vois, au fond. Le cheval reste contre la jambe, tout sage. La cale a tenu le mot. On a regardé ensemble.</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -4942,7 +4942,7 @@
 enfant-m|Je la vois, au fond.
 narrateur|Le cheval reste contre la jambe, tout sage.
 papa|La cale a tenu le mot.
-maman|Vous avez regardé ensemble.</t>
+maman|On a regardé ensemble.</t>
         </is>
       </c>
     </row>
@@ -5143,12 +5143,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Le cheval arrive sous l'étagère. Le cheval lève le nez, trop bas encore. Tout en haut ? Tout en haut, près du. Papa s'arrête, les lèvres encore rondes. Près du pot ? Nino garde sa bouche fermée, après. Le haut est trop loin, pour lui. Un tabouret dort près du mur. Vous faites quoi, alors ?</t>
+          <t>Le cheval arrive sous l'étagère. Le cheval lève le nez, trop bas encore. Tout en haut ? Tout en haut, près du. Papa s'arrête, les lèvres encore rondes. Près du pot ? Nino garde sa bouche fermée, après. Le haut est trop loin, pour lui. Un tabouret dort près du mur. Tu fais quoi, alors ?</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Le cheval arrive sous l'étagère. Le cheval lève le nez, trop bas encore. Tout en haut ? Tout en haut, près du. Papa s'arrête, les lèvres encore rondes. Près du pot ? Nino garde sa bouche fermée, après. Le haut est trop loin, pour lui. Un tabouret dort près du mur. Vous faites quoi, alors ?</t>
+          <t>Le cheval arrive sous l'étagère. Le cheval lève le nez, trop bas encore. Tout en haut ? Tout en haut, près du. Papa s'arrête, les lèvres encore rondes. Près du pot ? Nino garde sa bouche fermée, après. Le haut est trop loin, pour lui. Un tabouret dort près du mur. Tu fais quoi, alors ?</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5292,7 +5292,7 @@
 narrateur|Nino garde sa bouche fermée, après.
 maman|Le haut est trop loin, pour lui.
 papa|Un tabouret dort près du mur.
-papa|Vous faites quoi, alors ?</t>
+papa|Tu fais quoi, alors ?</t>
         </is>
       </c>
     </row>
@@ -6927,12 +6927,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>La boîte. Oui. Le cheval penche déjà sous le bras. Le chiffon dort dans la poche. Le métal a un peu sonné. J'écoute la suite. Vous restez ensemble.</t>
+          <t>La boîte. Oui. Le cheval penche déjà sous le bras. Le chiffon dort dans la poche. Le métal a un peu sonné. J'écoute la suite. On reste ensemble.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>La boîte. Oui. Le cheval penche déjà sous le bras. Le chiffon dort dans la poche. Le métal a un peu sonné. J'écoute la suite. Vous restez ensemble.</t>
+          <t>La boîte. Oui. Le cheval penche déjà sous le bras. Le chiffon dort dans la poche. Le métal a un peu sonné. J'écoute la suite. On reste ensemble.</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -7077,7 +7077,7 @@
 narrateur|Le chiffon dort dans la poche.
 papa|Le métal a un peu sonné.
 enfant-m|J'écoute la suite.
-maman|Vous restez ensemble.</t>
+maman|On reste ensemble.</t>
         </is>
       </c>
     </row>
@@ -7297,12 +7297,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>La boîte arrive près de l'établi. La boîte glisse sur une planche, tout fin. Des copeaux cachent les tiroirs, tout jaunes. C'est ici ? C'est le tiroir. Le mot s'arrête au milieu. Lequel ? Nino referme sa bouche, tout net. Les tiroirs se ressemblent tous. Vous faites comment, tous les deux ?</t>
+          <t>La boîte arrive près de l'établi. La boîte glisse sur une planche, tout fin. Des copeaux cachent les tiroirs, tout jaunes. C'est ici ? C'est le tiroir. Le mot s'arrête au milieu. Lequel ? Nino referme sa bouche, tout net. Les tiroirs se ressemblent tous. On fait comment, Nino ?</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>La boîte arrive près de l'établi. La boîte glisse sur une planche, tout fin. Des copeaux cachent les tiroirs, tout jaunes. C'est ici ? C'est le tiroir. Le mot s'arrête au milieu. Lequel ? Nino referme sa bouche, tout net. Les tiroirs se ressemblent tous. Vous faites comment, tous les deux ?</t>
+          <t>La boîte arrive près de l'établi. La boîte glisse sur une planche, tout fin. Des copeaux cachent les tiroirs, tout jaunes. C'est ici ? C'est le tiroir. Le mot s'arrête au milieu. Lequel ? Nino referme sa bouche, tout net. Les tiroirs se ressemblent tous. On fait comment, Nino ?</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -7446,7 +7446,7 @@
 enfant-m|Lequel ?
 narrateur|Nino referme sa bouche, tout net.
 maman|Les tiroirs se ressemblent tous.
-papa|Vous faites comment, tous les deux ?</t>
+papa|On fait comment, Nino ?</t>
         </is>
       </c>
     </row>
@@ -8542,12 +8542,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>La roue du bas tient, tout nette. On s'est baissés, papa. Le haut gardera son ombre. Lavez-vous les mains, tout doux. La boîte ronde garde une poussière, tout fine. Nino tapote le dos, tout léger. Le bois a un peu de poussière. Une abeille passe, puis l'auvent se tait.</t>
+          <t>La roue du bas tient, tout nette. On s'est baissés, papa. Le haut gardera son ombre. Lave-toi les mains, tout doux. La boîte ronde garde une poussière, tout fine. Nino tapote le dos, tout léger. Le bois a un peu de poussière. Une abeille passe, puis l'auvent se tait.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>La roue du bas tient, tout nette. On s'est baissés, papa. Le haut gardera son ombre. Lavez-vous les mains, tout doux. La boîte ronde garde une poussière, tout fine. Nino tapote le dos, tout léger. Le bois a un peu de poussière. Une abeille passe, puis l'auvent se tait.</t>
+          <t>La roue du bas tient, tout nette. On s'est baissés, papa. Le haut gardera son ombre. Lave-toi les mains, tout doux. La boîte ronde garde une poussière, tout fine. Nino tapote le dos, tout léger. Le bois a un peu de poussière. Une abeille passe, puis l'auvent se tait.</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -8685,7 +8685,7 @@
           <t>narrateur|La roue du bas tient, tout nette.
 enfant-m|On s'est baissés, papa.
 papa|Le haut gardera son ombre.
-maman|Lavez-vous les mains, tout doux.
+maman|Lave-toi les mains, tout doux.
 narrateur|La boîte ronde garde une poussière, tout fine.
 narrateur|Nino tapote le dos, tout léger.
 narrateur|Le bois a un peu de poussière.
@@ -8716,12 +8716,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>La boîte arrive près du coffre. La boîte tape le bois, un petit toc. Elle est là-dedans ? Elle est dans le. Maman cherche, un doigt en l'air. Le couvercle ne bouge pas, encore. Ouvre ! Nino recule d'un pas, puis attend. Le bois est trop lourd, tout seul. Vous trouvez comment ?</t>
+          <t>La boîte arrive près du coffre. La boîte tape le bois, un petit toc. Elle est là-dedans ? Elle est dans le. Maman cherche, un doigt en l'air. Le couvercle ne bouge pas, encore. Ouvre ! Nino recule d'un pas, puis attend. Le bois est trop lourd, tout seul. Tu trouves comment ?</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>La boîte arrive près du coffre. La boîte tape le bois, un petit toc. Elle est là-dedans ? Elle est dans le. Maman cherche, un doigt en l'air. Le couvercle ne bouge pas, encore. Ouvre ! Nino recule d'un pas, puis attend. Le bois est trop lourd, tout seul. Vous trouvez comment ?</t>
+          <t>La boîte arrive près du coffre. La boîte tape le bois, un petit toc. Elle est là-dedans ? Elle est dans le. Maman cherche, un doigt en l'air. Le couvercle ne bouge pas, encore. Ouvre ! Nino recule d'un pas, puis attend. Le bois est trop lourd, tout seul. Tu trouves comment ?</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -8865,7 +8865,7 @@
 enfant-m|Ouvre !
 narrateur|Nino recule d'un pas, puis attend.
 papa|Le bois est trop lourd, tout seul.
-maman|Vous trouvez comment ?</t>
+maman|Tu trouves comment ?</t>
         </is>
       </c>
     </row>
@@ -9436,12 +9436,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>À deux. Tes mains ici, les miennes là. Le couvercle s'ouvre, tout lent. Dans le. Nino attend, les lèvres fermées. Dans le coin. La boîte attend un dernier toc. Vous avez porté ensemble. La suite a eu sa place.</t>
+          <t>À deux. Tes mains ici, les miennes là. Le couvercle s'ouvre, tout lent. Dans le. Nino attend, les lèvres fermées. Dans le coin. La boîte attend un dernier toc. On a porté ensemble. La suite a eu sa place.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>À deux. Tes mains ici, les miennes là. Le couvercle s'ouvre, tout lent. Dans le. Nino attend, les lèvres fermées. Dans le coin. La boîte attend un dernier toc. Vous avez porté ensemble. La suite a eu sa place.</t>
+          <t>À deux. Tes mains ici, les miennes là. Le couvercle s'ouvre, tout lent. Dans le. Nino attend, les lèvres fermées. Dans le coin. La boîte attend un dernier toc. On a porté ensemble. La suite a eu sa place.</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -9583,7 +9583,7 @@
 narrateur|Nino attend, les lèvres fermées.
 maman|Dans le coin.
 narrateur|La boîte attend un dernier toc.
-papa|Vous avez porté ensemble.
+papa|On a porté ensemble.
 maman|La suite a eu sa place.</t>
         </is>
       </c>
@@ -9611,12 +9611,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>À deux, le coffre a parlé, enfin. On a porté, tous les deux. Tes mains étaient à la bonne place. Le pain vous attend. La boîte ronde garde une poussière, tout fine. Nino essuie une main sur son pantalon. Un grain de savon reste sur le bois. Le cheval avance, roue après roue.</t>
+          <t>À deux, le coffre a parlé, enfin. On a porté, tous les deux. Tes mains étaient à la bonne place. Le pain t'attend. La boîte ronde garde une poussière, tout fine. Nino essuie une main sur son pantalon. Un grain de savon reste sur le bois. Le cheval avance, roue après roue.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>À deux, le coffre a parlé, enfin. On a porté, tous les deux. Tes mains étaient à la bonne place. Le pain vous attend. La boîte ronde garde une poussière, tout fine. Nino essuie une main sur son pantalon. Un grain de savon reste sur le bois. Le cheval avance, roue après roue.</t>
+          <t>À deux, le coffre a parlé, enfin. On a porté, tous les deux. Tes mains étaient à la bonne place. Le pain t'attend. La boîte ronde garde une poussière, tout fine. Nino essuie une main sur son pantalon. Un grain de savon reste sur le bois. Le cheval avance, roue après roue.</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -9754,7 +9754,7 @@
           <t>narrateur|À deux, le coffre a parlé, enfin.
 enfant-m|On a porté, tous les deux.
 papa|Tes mains étaient à la bonne place.
-maman|Le pain vous attend.
+maman|Le pain t'attend.
 narrateur|La boîte ronde garde une poussière, tout fine.
 narrateur|Nino essuie une main sur son pantalon.
 narrateur|Un grain de savon reste sur le bois.
@@ -9785,12 +9785,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>La cale, dessous. Je glisse le bois, tout doux. Le couvercle reste ouvert, un peu. À gauche. Nino tourne la tête, sans parler. Je la vois, au fond. La boîte attend un dernier toc. La cale a tenu le mot. Vous avez regardé ensemble.</t>
+          <t>La cale, dessous. Je glisse le bois, tout doux. Le couvercle reste ouvert, un peu. À gauche. Nino tourne la tête, sans parler. Je la vois, au fond. La boîte attend un dernier toc. La cale a tenu le mot. On a regardé ensemble.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>La cale, dessous. Je glisse le bois, tout doux. Le couvercle reste ouvert, un peu. À gauche. Nino tourne la tête, sans parler. Je la vois, au fond. La boîte attend un dernier toc. La cale a tenu le mot. Vous avez regardé ensemble.</t>
+          <t>La cale, dessous. Je glisse le bois, tout doux. Le couvercle reste ouvert, un peu. À gauche. Nino tourne la tête, sans parler. Je la vois, au fond. La boîte attend un dernier toc. La cale a tenu le mot. On a regardé ensemble.</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -9933,7 +9933,7 @@
 enfant-m|Je la vois, au fond.
 narrateur|La boîte attend un dernier toc.
 papa|La cale a tenu le mot.
-maman|Vous avez regardé ensemble.</t>
+maman|On a regardé ensemble.</t>
         </is>
       </c>
     </row>
@@ -10134,12 +10134,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>La boîte arrive sous l'étagère. La boîte n'atteint pas le bord, trop haute. Tout en haut ? Tout en haut, près du. Papa s'arrête, les lèvres encore rondes. Près du pot ? Nino garde sa bouche fermée, après. Le haut est trop loin, pour lui. Un tabouret dort près du mur. Vous faites quoi, alors ?</t>
+          <t>La boîte arrive sous l'étagère. La boîte n'atteint pas le bord, trop haute. Tout en haut ? Tout en haut, près du. Papa s'arrête, les lèvres encore rondes. Près du pot ? Nino garde sa bouche fermée, après. Le haut est trop loin, pour lui. Un tabouret dort près du mur. Tu fais quoi, alors ?</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>La boîte arrive sous l'étagère. La boîte n'atteint pas le bord, trop haute. Tout en haut ? Tout en haut, près du. Papa s'arrête, les lèvres encore rondes. Près du pot ? Nino garde sa bouche fermée, après. Le haut est trop loin, pour lui. Un tabouret dort près du mur. Vous faites quoi, alors ?</t>
+          <t>La boîte arrive sous l'étagère. La boîte n'atteint pas le bord, trop haute. Tout en haut ? Tout en haut, près du. Papa s'arrête, les lèvres encore rondes. Près du pot ? Nino garde sa bouche fermée, après. Le haut est trop loin, pour lui. Un tabouret dort près du mur. Tu fais quoi, alors ?</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -10283,7 +10283,7 @@
 narrateur|Nino garde sa bouche fermée, après.
 maman|Le haut est trop loin, pour lui.
 papa|Un tabouret dort près du mur.
-papa|Vous faites quoi, alors ?</t>
+papa|Tu fais quoi, alors ?</t>
         </is>
       </c>
     </row>
@@ -12288,12 +12288,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Le chiffon arrive près de l'établi. Le chiffon s'accroche à une écharde. Des copeaux cachent les tiroirs, tout jaunes. C'est ici ? C'est le tiroir. Le mot s'arrête au milieu. Lequel ? Nino referme sa bouche, tout net. Les tiroirs se ressemblent tous. Vous faites comment, tous les deux ?</t>
+          <t>Le chiffon arrive près de l'établi. Le chiffon s'accroche à une écharde. Des copeaux cachent les tiroirs, tout jaunes. C'est ici ? C'est le tiroir. Le mot s'arrête au milieu. Lequel ? Nino referme sa bouche, tout net. Les tiroirs se ressemblent tous. On fait comment, Nino ?</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Le chiffon arrive près de l'établi. Le chiffon s'accroche à une écharde. Des copeaux cachent les tiroirs, tout jaunes. C'est ici ? C'est le tiroir. Le mot s'arrête au milieu. Lequel ? Nino referme sa bouche, tout net. Les tiroirs se ressemblent tous. Vous faites comment, tous les deux ?</t>
+          <t>Le chiffon arrive près de l'établi. Le chiffon s'accroche à une écharde. Des copeaux cachent les tiroirs, tout jaunes. C'est ici ? C'est le tiroir. Le mot s'arrête au milieu. Lequel ? Nino referme sa bouche, tout net. Les tiroirs se ressemblent tous. On fait comment, Nino ?</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -12437,7 +12437,7 @@
 enfant-m|Lequel ?
 narrateur|Nino referme sa bouche, tout net.
 maman|Les tiroirs se ressemblent tous.
-papa|Vous faites comment, tous les deux ?</t>
+papa|On fait comment, Nino ?</t>
         </is>
       </c>
     </row>
@@ -13533,12 +13533,12 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>La roue du bas tient, tout nette. On s'est baissés, papa. Le haut gardera son ombre. Lavez-vous les mains, tout doux. Le chiffon sent encore le savon du bois. Nino tapote le dos, tout léger. Le bois a un peu de poussière. Une abeille passe, puis l'auvent se tait.</t>
+          <t>La roue du bas tient, tout nette. On s'est baissés, papa. Le haut gardera son ombre. Lave-toi les mains, tout doux. Le chiffon sent encore le savon du bois. Nino tapote le dos, tout léger. Le bois a un peu de poussière. Une abeille passe, puis l'auvent se tait.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>La roue du bas tient, tout nette. On s'est baissés, papa. Le haut gardera son ombre. Lavez-vous les mains, tout doux. Le chiffon sent encore le savon du bois. Nino tapote le dos, tout léger. Le bois a un peu de poussière. Une abeille passe, puis l'auvent se tait.</t>
+          <t>La roue du bas tient, tout nette. On s'est baissés, papa. Le haut gardera son ombre. Lave-toi les mains, tout doux. Le chiffon sent encore le savon du bois. Nino tapote le dos, tout léger. Le bois a un peu de poussière. Une abeille passe, puis l'auvent se tait.</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -13676,7 +13676,7 @@
           <t>narrateur|La roue du bas tient, tout nette.
 enfant-m|On s'est baissés, papa.
 papa|Le haut gardera son ombre.
-maman|Lavez-vous les mains, tout doux.
+maman|Lave-toi les mains, tout doux.
 narrateur|Le chiffon sent encore le savon du bois.
 narrateur|Nino tapote le dos, tout léger.
 narrateur|Le bois a un peu de poussière.
@@ -13707,12 +13707,12 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Le chiffon arrive près du coffre. Le chiffon glisse sous le bord, déjà. Elle est là-dedans ? Elle est dans le. Maman cherche, un doigt en l'air. Le couvercle ne bouge pas, encore. Ouvre ! Nino recule d'un pas, puis attend. Le bois est trop lourd, tout seul. Vous trouvez comment ?</t>
+          <t>Le chiffon arrive près du coffre. Le chiffon glisse sous le bord, déjà. Elle est là-dedans ? Elle est dans le. Maman cherche, un doigt en l'air. Le couvercle ne bouge pas, encore. Ouvre ! Nino recule d'un pas, puis attend. Le bois est trop lourd, tout seul. Tu trouves comment ?</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Le chiffon arrive près du coffre. Le chiffon glisse sous le bord, déjà. Elle est là-dedans ? Elle est dans le. Maman cherche, un doigt en l'air. Le couvercle ne bouge pas, encore. Ouvre ! Nino recule d'un pas, puis attend. Le bois est trop lourd, tout seul. Vous trouvez comment ?</t>
+          <t>Le chiffon arrive près du coffre. Le chiffon glisse sous le bord, déjà. Elle est là-dedans ? Elle est dans le. Maman cherche, un doigt en l'air. Le couvercle ne bouge pas, encore. Ouvre ! Nino recule d'un pas, puis attend. Le bois est trop lourd, tout seul. Tu trouves comment ?</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
@@ -13856,7 +13856,7 @@
 enfant-m|Ouvre !
 narrateur|Nino recule d'un pas, puis attend.
 papa|Le bois est trop lourd, tout seul.
-maman|Vous trouvez comment ?</t>
+maman|Tu trouves comment ?</t>
         </is>
       </c>
     </row>
@@ -14427,12 +14427,12 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>À deux. Tes mains ici, les miennes là. Le couvercle s'ouvre, tout lent. Dans le. Nino attend, les lèvres fermées. Dans le coin. Le chiffon dort contre sa paume. Vous avez porté ensemble. La suite a eu sa place.</t>
+          <t>À deux. Tes mains ici, les miennes là. Le couvercle s'ouvre, tout lent. Dans le. Nino attend, les lèvres fermées. Dans le coin. Le chiffon dort contre sa paume. On a porté ensemble. La suite a eu sa place.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>À deux. Tes mains ici, les miennes là. Le couvercle s'ouvre, tout lent. Dans le. Nino attend, les lèvres fermées. Dans le coin. Le chiffon dort contre sa paume. Vous avez porté ensemble. La suite a eu sa place.</t>
+          <t>À deux. Tes mains ici, les miennes là. Le couvercle s'ouvre, tout lent. Dans le. Nino attend, les lèvres fermées. Dans le coin. Le chiffon dort contre sa paume. On a porté ensemble. La suite a eu sa place.</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
@@ -14574,7 +14574,7 @@
 narrateur|Nino attend, les lèvres fermées.
 maman|Dans le coin.
 narrateur|Le chiffon dort contre sa paume.
-papa|Vous avez porté ensemble.
+papa|On a porté ensemble.
 maman|La suite a eu sa place.</t>
         </is>
       </c>
@@ -14602,12 +14602,12 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>À deux, le coffre a parlé, enfin. On a porté, tous les deux. Tes mains étaient à la bonne place. Le pain vous attend. Le chiffon sent encore le savon du bois. Nino essuie une main sur son pantalon. Un grain de savon reste sur le bois. Le cheval avance, roue après roue.</t>
+          <t>À deux, le coffre a parlé, enfin. On a porté, tous les deux. Tes mains étaient à la bonne place. Le pain t'attend. Le chiffon sent encore le savon du bois. Nino essuie une main sur son pantalon. Un grain de savon reste sur le bois. Le cheval avance, roue après roue.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>À deux, le coffre a parlé, enfin. On a porté, tous les deux. Tes mains étaient à la bonne place. Le pain vous attend. Le chiffon sent encore le savon du bois. Nino essuie une main sur son pantalon. Un grain de savon reste sur le bois. Le cheval avance, roue après roue.</t>
+          <t>À deux, le coffre a parlé, enfin. On a porté, tous les deux. Tes mains étaient à la bonne place. Le pain t'attend. Le chiffon sent encore le savon du bois. Nino essuie une main sur son pantalon. Un grain de savon reste sur le bois. Le cheval avance, roue après roue.</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
@@ -14745,7 +14745,7 @@
           <t>narrateur|À deux, le coffre a parlé, enfin.
 enfant-m|On a porté, tous les deux.
 papa|Tes mains étaient à la bonne place.
-maman|Le pain vous attend.
+maman|Le pain t'attend.
 narrateur|Le chiffon sent encore le savon du bois.
 narrateur|Nino essuie une main sur son pantalon.
 narrateur|Un grain de savon reste sur le bois.
@@ -14776,12 +14776,12 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>La cale, dessous. Je glisse le bois, tout doux. Le couvercle reste ouvert, un peu. À gauche. Nino tourne la tête, sans parler. Je la vois, au fond. Le chiffon dort contre sa paume. La cale a tenu le mot. Vous avez regardé ensemble.</t>
+          <t>La cale, dessous. Je glisse le bois, tout doux. Le couvercle reste ouvert, un peu. À gauche. Nino tourne la tête, sans parler. Je la vois, au fond. Le chiffon dort contre sa paume. La cale a tenu le mot. On a regardé ensemble.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>La cale, dessous. Je glisse le bois, tout doux. Le couvercle reste ouvert, un peu. À gauche. Nino tourne la tête, sans parler. Je la vois, au fond. Le chiffon dort contre sa paume. La cale a tenu le mot. Vous avez regardé ensemble.</t>
+          <t>La cale, dessous. Je glisse le bois, tout doux. Le couvercle reste ouvert, un peu. À gauche. Nino tourne la tête, sans parler. Je la vois, au fond. Le chiffon dort contre sa paume. La cale a tenu le mot. On a regardé ensemble.</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
@@ -14924,7 +14924,7 @@
 enfant-m|Je la vois, au fond.
 narrateur|Le chiffon dort contre sa paume.
 papa|La cale a tenu le mot.
-maman|Vous avez regardé ensemble.</t>
+maman|On a regardé ensemble.</t>
         </is>
       </c>
     </row>
@@ -15125,12 +15125,12 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Le chiffon arrive sous l'étagère. Le chiffon pend, trop court, sous le bois. Tout en haut ? Tout en haut, près du. Papa s'arrête, les lèvres encore rondes. Près du pot ? Nino garde sa bouche fermée, après. Le haut est trop loin, pour lui. Un tabouret dort près du mur. Vous faites quoi, alors ?</t>
+          <t>Le chiffon arrive sous l'étagère. Le chiffon pend, trop court, sous le bois. Tout en haut ? Tout en haut, près du. Papa s'arrête, les lèvres encore rondes. Près du pot ? Nino garde sa bouche fermée, après. Le haut est trop loin, pour lui. Un tabouret dort près du mur. Tu fais quoi, alors ?</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Le chiffon arrive sous l'étagère. Le chiffon pend, trop court, sous le bois. Tout en haut ? Tout en haut, près du. Papa s'arrête, les lèvres encore rondes. Près du pot ? Nino garde sa bouche fermée, après. Le haut est trop loin, pour lui. Un tabouret dort près du mur. Vous faites quoi, alors ?</t>
+          <t>Le chiffon arrive sous l'étagère. Le chiffon pend, trop court, sous le bois. Tout en haut ? Tout en haut, près du. Papa s'arrête, les lèvres encore rondes. Près du pot ? Nino garde sa bouche fermée, après. Le haut est trop loin, pour lui. Un tabouret dort près du mur. Tu fais quoi, alors ?</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
@@ -15274,7 +15274,7 @@
 narrateur|Nino garde sa bouche fermée, après.
 maman|Le haut est trop loin, pour lui.
 papa|Un tabouret dort près du mur.
-papa|Vous faites quoi, alors ?</t>
+papa|Tu fais quoi, alors ?</t>
         </is>
       </c>
     </row>
@@ -16537,7 +16537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16636,6 +16636,13 @@
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
